--- a/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643B6A79-7A03-4F7D-8499-93C498CC9ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D2A9A9-29EB-49FF-9DB3-E7CF259D6684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,7 +486,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
+        <f>(MAX(B:B)-MIN(B:B))/(MODE(D:D)-MIN(D:D))</f>
         <v>0.76049999999999995</v>
       </c>
       <c r="H2">
@@ -511,12 +511,12 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))</f>
         <v>96</v>
       </c>
       <c r="H3">
-        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))*1</f>
-        <v>96</v>
+        <f>0.675*(INDEX(A:A,MATCH(MAX(B:B)*0.853,B:B))-INDEX(A:A,MATCH(MAX(B:B)*0.353,B:B)))</f>
+        <v>155.92500000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -536,12 +536,12 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
+        <f>INDEX(A:A, MATCH(MIN(B:B)*1.02, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))</f>
         <v>8</v>
       </c>
       <c r="H4">
-        <f>INDEX(A:A, MATCH(MIN(B:B)*1.02, B:B)) - (INDEX(A:A, MATCH(MODE(D:D), D:D, 0)))</f>
-        <v>8</v>
+        <f>ABS(1.294*(INDEX(A:A,MATCH(MAX(B:B)*0.353,B:B)))-0.294*(INDEX(A:A,MATCH(MAX(B:B)*0.853,B:B)))-INDEX(A:A,MATCH(MODE(D:D),D:D,0)))</f>
+        <v>42.914000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -556,6 +556,10 @@
       </c>
       <c r="D5">
         <v>0</v>
+      </c>
+      <c r="G5">
+        <f>INDEX(A:A, MATCH(MODE(D:D), D:D,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D2A9A9-29EB-49FF-9DB3-E7CF259D6684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BE849E-6DAC-462E-9BC8-0617BCDAD14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,8 +511,8 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))</f>
-        <v>96</v>
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - G4</f>
+        <v>120</v>
       </c>
       <c r="H3">
         <f>0.675*(INDEX(A:A,MATCH(MAX(B:B)*0.853,B:B))-INDEX(A:A,MATCH(MAX(B:B)*0.353,B:B)))</f>
@@ -588,6 +588,10 @@
       </c>
       <c r="D7">
         <v>100</v>
+      </c>
+      <c r="G7">
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B))</f>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
